--- a/src/tablescan_local/default_templates/staircase_portrait.xlsx
+++ b/src/tablescan_local/default_templates/staircase_portrait.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Staircase portrait" sheetId="1" ns1:id="Rc2ba1dfc72ab4199"/>
+    <sheet name="Staircase portrait" sheetId="1" ns1:id="Rdcf453904e8c4640"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Staircase portrait'!$A$1:$Q$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Staircase portrait'!$A$1:$Q$37</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -64,8 +64,23 @@
         <x:fgColor rgb="FFFCE2CB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEEEEE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCEBF9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE2CB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="15">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
@@ -86,11 +101,75 @@
         <x:color rgb="FF333333"/>
       </x:bottom>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="none"/>
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="none"/>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -137,6 +216,63 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -422,156 +558,143 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="4" t="str">
+      <c r="A4" s="23" t="str">
         <v>Date</v>
       </c>
-      <c r="B4" s="4" t="str">
+      <c r="B4" s="24" t="str">
         <v>Date</v>
       </c>
-      <c r="C4" s="4" t="str">
+      <c r="C4" s="25" t="str">
         <v>Date</v>
       </c>
-      <c r="D4" s="4" t="str">
+      <c r="D4" s="23" t="str">
         <v>Session</v>
       </c>
-      <c r="E4" s="4" t="str">
+      <c r="E4" s="24" t="str">
         <v>Session</v>
       </c>
-      <c r="F4" s="4" t="str">
+      <c r="F4" s="25" t="str">
         <v>Session</v>
       </c>
-      <c r="G4" s="4" t="str">
+      <c r="G4" s="23" t="str">
         <v>Operator</v>
       </c>
-      <c r="H4" s="4" t="str">
+      <c r="H4" s="24" t="str">
         <v>Operator</v>
       </c>
-      <c r="I4" s="4" t="str">
+      <c r="I4" s="24" t="str">
         <v>Operator</v>
       </c>
-      <c r="J4" s="4" t="str">
+      <c r="J4" s="24" t="str">
         <v>Operator</v>
       </c>
-      <c r="K4" s="4" t="str">
+      <c r="K4" s="24" t="str">
         <v>Operator</v>
       </c>
-      <c r="L4" s="4" t="str">
+      <c r="L4" s="25" t="str">
         <v>Operator</v>
       </c>
-      <c r="M4" s="4" t="str">
-        <v>Operator</v>
-      </c>
-      <c r="N4" s="4" t="str">
-        <v>Operator</v>
-      </c>
-      <c r="O4" s="4" t="str">
-        <v>Operator</v>
-      </c>
-      <c r="P4" s="4" t="str">
-        <v>Operator</v>
-      </c>
-      <c r="Q4" s="4" t="str">
-        <v>Operator</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="11" t="str">
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5" ht="29" customHeight="1">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="28"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6" ht="3" customHeight="1">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="31" t="str">
         <v>ID</v>
       </c>
-      <c r="B6" s="12" t="str">
+      <c r="B7" s="34" t="str">
         <v>L1</v>
       </c>
-      <c r="C6" s="12" t="str">
+      <c r="C7" s="34" t="str">
         <v>L2</v>
       </c>
-      <c r="D6" s="12" t="str">
+      <c r="D7" s="34" t="str">
         <v>L3</v>
       </c>
-      <c r="E6" s="12" t="str">
+      <c r="E7" s="34" t="str">
         <v>L4</v>
       </c>
-      <c r="F6" s="12" t="str">
+      <c r="F7" s="34" t="str">
         <v>L5</v>
       </c>
-      <c r="G6" s="12" t="str">
+      <c r="G7" s="34" t="str">
         <v>L6</v>
       </c>
-      <c r="H6" s="12" t="str">
+      <c r="H7" s="34" t="str">
         <v>L7</v>
       </c>
-      <c r="I6" s="12" t="str">
+      <c r="I7" s="34" t="str">
         <v>L drop</v>
       </c>
-      <c r="J6" s="13" t="str">
+      <c r="J7" s="35" t="str">
         <v>R1</v>
       </c>
-      <c r="K6" s="13" t="str">
+      <c r="K7" s="35" t="str">
         <v>R2</v>
       </c>
-      <c r="L6" s="13" t="str">
+      <c r="L7" s="35" t="str">
         <v>R3</v>
       </c>
-      <c r="M6" s="13" t="str">
+      <c r="M7" s="35" t="str">
         <v>R4</v>
       </c>
-      <c r="N6" s="13" t="str">
+      <c r="N7" s="35" t="str">
         <v>R5</v>
       </c>
-      <c r="O6" s="13" t="str">
+      <c r="O7" s="35" t="str">
         <v>R6</v>
       </c>
-      <c r="P6" s="13" t="str">
+      <c r="P7" s="35" t="str">
         <v>R7</v>
       </c>
-      <c r="Q6" s="13" t="str">
+      <c r="Q7" s="35" t="str">
         <v>R drop</v>
       </c>
-    </row>
-    <row r="7" ht="22.200000762939453" customHeight="1">
-      <c r="A7" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>1</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
     </row>
     <row r="8" ht="22.200000762939453" customHeight="1">
       <c r="A8" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>2</v>
+        <f>ROW()-7</f>
+        <v>1</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -592,8 +715,8 @@
     </row>
     <row r="9" ht="22.200000762939453" customHeight="1">
       <c r="A9" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>3</v>
+        <f>ROW()-7</f>
+        <v>2</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -614,8 +737,8 @@
     </row>
     <row r="10" ht="22.200000762939453" customHeight="1">
       <c r="A10" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>4</v>
+        <f>ROW()-7</f>
+        <v>3</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -636,8 +759,8 @@
     </row>
     <row r="11" ht="22.200000762939453" customHeight="1">
       <c r="A11" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>5</v>
+        <f>ROW()-7</f>
+        <v>4</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -658,8 +781,8 @@
     </row>
     <row r="12" ht="22.200000762939453" customHeight="1">
       <c r="A12" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>6</v>
+        <f>ROW()-7</f>
+        <v>5</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -680,8 +803,8 @@
     </row>
     <row r="13" ht="22.200000762939453" customHeight="1">
       <c r="A13" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>7</v>
+        <f>ROW()-7</f>
+        <v>6</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -702,8 +825,8 @@
     </row>
     <row r="14" ht="22.200000762939453" customHeight="1">
       <c r="A14" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>8</v>
+        <f>ROW()-7</f>
+        <v>7</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -724,8 +847,8 @@
     </row>
     <row r="15" ht="22.200000762939453" customHeight="1">
       <c r="A15" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>9</v>
+        <f>ROW()-7</f>
+        <v>8</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -746,8 +869,8 @@
     </row>
     <row r="16" ht="22.200000762939453" customHeight="1">
       <c r="A16" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>10</v>
+        <f>ROW()-7</f>
+        <v>9</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -768,8 +891,8 @@
     </row>
     <row r="17" ht="22.200000762939453" customHeight="1">
       <c r="A17" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>11</v>
+        <f>ROW()-7</f>
+        <v>10</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -790,8 +913,8 @@
     </row>
     <row r="18" ht="22.200000762939453" customHeight="1">
       <c r="A18" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>12</v>
+        <f>ROW()-7</f>
+        <v>11</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -812,8 +935,8 @@
     </row>
     <row r="19" ht="22.200000762939453" customHeight="1">
       <c r="A19" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>13</v>
+        <f>ROW()-7</f>
+        <v>12</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -834,8 +957,8 @@
     </row>
     <row r="20" ht="22.200000762939453" customHeight="1">
       <c r="A20" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>14</v>
+        <f>ROW()-7</f>
+        <v>13</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -856,8 +979,8 @@
     </row>
     <row r="21" ht="22.200000762939453" customHeight="1">
       <c r="A21" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>15</v>
+        <f>ROW()-7</f>
+        <v>14</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -878,8 +1001,8 @@
     </row>
     <row r="22" ht="22.200000762939453" customHeight="1">
       <c r="A22" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>16</v>
+        <f>ROW()-7</f>
+        <v>15</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -900,8 +1023,8 @@
     </row>
     <row r="23" ht="22.200000762939453" customHeight="1">
       <c r="A23" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>17</v>
+        <f>ROW()-7</f>
+        <v>16</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -922,8 +1045,8 @@
     </row>
     <row r="24" ht="22.200000762939453" customHeight="1">
       <c r="A24" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>18</v>
+        <f>ROW()-7</f>
+        <v>17</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -944,8 +1067,8 @@
     </row>
     <row r="25" ht="22.200000762939453" customHeight="1">
       <c r="A25" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>19</v>
+        <f>ROW()-7</f>
+        <v>18</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -966,8 +1089,8 @@
     </row>
     <row r="26" ht="22.200000762939453" customHeight="1">
       <c r="A26" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>20</v>
+        <f>ROW()-7</f>
+        <v>19</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -988,8 +1111,8 @@
     </row>
     <row r="27" ht="22.200000762939453" customHeight="1">
       <c r="A27" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>21</v>
+        <f>ROW()-7</f>
+        <v>20</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -1010,8 +1133,8 @@
     </row>
     <row r="28" ht="22.200000762939453" customHeight="1">
       <c r="A28" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>22</v>
+        <f>ROW()-7</f>
+        <v>21</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -1032,8 +1155,8 @@
     </row>
     <row r="29" ht="22.200000762939453" customHeight="1">
       <c r="A29" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>23</v>
+        <f>ROW()-7</f>
+        <v>22</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -1054,8 +1177,8 @@
     </row>
     <row r="30" ht="22.200000762939453" customHeight="1">
       <c r="A30" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>24</v>
+        <f>ROW()-7</f>
+        <v>23</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -1076,8 +1199,8 @@
     </row>
     <row r="31" ht="22.200000762939453" customHeight="1">
       <c r="A31" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>25</v>
+        <f>ROW()-7</f>
+        <v>24</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -1098,8 +1221,8 @@
     </row>
     <row r="32" ht="22.200000762939453" customHeight="1">
       <c r="A32" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>26</v>
+        <f>ROW()-7</f>
+        <v>25</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -1120,8 +1243,8 @@
     </row>
     <row r="33" ht="22.200000762939453" customHeight="1">
       <c r="A33" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>27</v>
+        <f>ROW()-7</f>
+        <v>26</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -1142,8 +1265,8 @@
     </row>
     <row r="34" ht="22.200000762939453" customHeight="1">
       <c r="A34" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>28</v>
+        <f>ROW()-7</f>
+        <v>27</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -1164,8 +1287,8 @@
     </row>
     <row r="35" ht="22.200000762939453" customHeight="1">
       <c r="A35" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>29</v>
+        <f>ROW()-7</f>
+        <v>28</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -1186,8 +1309,8 @@
     </row>
     <row r="36" ht="22.200000762939453" customHeight="1">
       <c r="A36" s="15" t="n">
-        <f>ROW()-6</f>
-        <v>30</v>
+        <f>ROW()-7</f>
+        <v>29</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -1206,6 +1329,28 @@
       <c r="P36" s="16"/>
       <c r="Q36" s="16"/>
     </row>
+    <row r="37" ht="22.200000762939453" customHeight="1">
+      <c r="A37" t="n">
+        <f>ROW()-7</f>
+        <v>30</v>
+      </c>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:Q1"/>
@@ -1213,8 +1358,8 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G4:Q4"/>
-    <mergeCell ref="G5:Q5"/>
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="G5:L5"/>
   </mergeCells>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>

--- a/src/tablescan_local/default_templates/staircase_portrait.xlsx
+++ b/src/tablescan_local/default_templates/staircase_portrait.xlsx
@@ -1330,26 +1330,26 @@
       <c r="Q36" s="16"/>
     </row>
     <row r="37" ht="22.200000762939453" customHeight="1">
-      <c r="A37" t="n">
+      <c r="A37" s="15" t="n">
         <f>ROW()-7</f>
         <v>30</v>
       </c>
-      <c r="B37"/>
-      <c r="C37"/>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37"/>
-      <c r="M37"/>
-      <c r="N37"/>
-      <c r="O37"/>
-      <c r="P37"/>
-      <c r="Q37"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
     </row>
   </sheetData>
   <mergeCells>
